--- a/Tables/Data/__enums__.xlsx
+++ b/Tables/Data/__enums__.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -667,6 +667,102 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EItemCategory</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>道具类别</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Clue</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>线索</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>线索：服务于「信息」的奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>关键物</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>关键物：推进剧情 / 解谜用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
